--- a/Final Results/Final Results.xlsx
+++ b/Final Results/Final Results.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Deepanshu Postdoc MSU\Research\GECCO 2025\2. Bench-iMCDM\Results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Deepanshu Postdoc MSU\Research\GECCO 2025\2. Bench-iMCDM\Source Code\Bench-iMCDM_GECCO26\Final Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{962B4EC8-8C2E-4BAE-B98A-D12D5CA49191}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -221,12 +221,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -237,6 +231,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -542,7 +542,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="19" t="s">
         <v>8</v>
       </c>
       <c r="C2" s="14" t="s">
@@ -571,7 +571,7 @@
       <c r="R2" s="14"/>
     </row>
     <row r="3" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B3" s="16"/>
+      <c r="B3" s="20"/>
       <c r="C3" s="1" t="s">
         <v>0</v>
       </c>
@@ -1067,7 +1067,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="18" t="s">
         <v>8</v>
       </c>
       <c r="C2" s="14" t="s">
@@ -1096,7 +1096,7 @@
       <c r="R2" s="14"/>
     </row>
     <row r="3" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B3" s="20"/>
+      <c r="B3" s="18"/>
       <c r="C3" s="1" t="s">
         <v>0</v>
       </c>
@@ -1147,7 +1147,7 @@
       </c>
     </row>
     <row r="4" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="15" t="s">
         <v>9</v>
       </c>
       <c r="C4" s="13">
@@ -1200,7 +1200,7 @@
       </c>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B5" s="17"/>
+      <c r="B5" s="15"/>
       <c r="C5" s="13">
         <v>6</v>
       </c>
@@ -1251,7 +1251,7 @@
       </c>
     </row>
     <row r="6" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B6" s="17"/>
+      <c r="B6" s="15"/>
       <c r="C6" s="13">
         <v>6</v>
       </c>
@@ -1302,7 +1302,7 @@
       </c>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B7" s="17"/>
+      <c r="B7" s="15"/>
       <c r="C7" s="13">
         <v>6</v>
       </c>
@@ -1422,7 +1422,7 @@
       </c>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="15" t="s">
         <v>10</v>
       </c>
       <c r="C9" s="13">
@@ -1475,7 +1475,7 @@
       </c>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B10" s="17"/>
+      <c r="B10" s="15"/>
       <c r="C10" s="13">
         <v>6</v>
       </c>
@@ -1526,7 +1526,7 @@
       </c>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B11" s="17"/>
+      <c r="B11" s="15"/>
       <c r="C11" s="13">
         <v>6</v>
       </c>
@@ -1577,7 +1577,7 @@
       </c>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B12" s="17"/>
+      <c r="B12" s="15"/>
       <c r="C12" s="13">
         <v>6</v>
       </c>
@@ -1681,7 +1681,7 @@
       </c>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="15" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="13">
@@ -1734,7 +1734,7 @@
       </c>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B15" s="17"/>
+      <c r="B15" s="15"/>
       <c r="C15" s="13">
         <v>5</v>
       </c>
@@ -1785,7 +1785,7 @@
       </c>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B16" s="17"/>
+      <c r="B16" s="15"/>
       <c r="C16" s="13">
         <v>6</v>
       </c>
@@ -1836,7 +1836,7 @@
       </c>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B17" s="17"/>
+      <c r="B17" s="15"/>
       <c r="C17" s="13">
         <v>5</v>
       </c>
@@ -1940,7 +1940,7 @@
       </c>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B19" s="17" t="s">
+      <c r="B19" s="15" t="s">
         <v>12</v>
       </c>
       <c r="C19" s="13">
@@ -1993,7 +1993,7 @@
       </c>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B20" s="17"/>
+      <c r="B20" s="15"/>
       <c r="C20" s="13">
         <v>8</v>
       </c>
@@ -2044,7 +2044,7 @@
       </c>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B21" s="17"/>
+      <c r="B21" s="15"/>
       <c r="C21" s="13">
         <v>7</v>
       </c>
@@ -2095,7 +2095,7 @@
       </c>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B22" s="17"/>
+      <c r="B22" s="15"/>
       <c r="C22" s="13">
         <v>8</v>
       </c>
@@ -2199,7 +2199,7 @@
       </c>
     </row>
     <row r="24" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B24" s="18" t="s">
+      <c r="B24" s="16" t="s">
         <v>13</v>
       </c>
       <c r="C24" s="13">
@@ -2252,7 +2252,7 @@
       </c>
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B25" s="18"/>
+      <c r="B25" s="16"/>
       <c r="C25" s="13">
         <v>4</v>
       </c>
@@ -2303,7 +2303,7 @@
       </c>
     </row>
     <row r="26" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B26" s="18"/>
+      <c r="B26" s="16"/>
       <c r="C26" s="13">
         <v>8</v>
       </c>
@@ -2354,7 +2354,7 @@
       </c>
     </row>
     <row r="27" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B27" s="18"/>
+      <c r="B27" s="16"/>
       <c r="C27" s="13">
         <v>3</v>
       </c>
@@ -2458,7 +2458,7 @@
       </c>
     </row>
     <row r="29" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B29" s="17" t="s">
+      <c r="B29" s="15" t="s">
         <v>18</v>
       </c>
       <c r="C29" s="13">
@@ -2511,7 +2511,7 @@
       </c>
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B30" s="17"/>
+      <c r="B30" s="15"/>
       <c r="C30" s="13">
         <v>5</v>
       </c>
@@ -2562,7 +2562,7 @@
       </c>
     </row>
     <row r="31" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B31" s="17"/>
+      <c r="B31" s="15"/>
       <c r="C31" s="13">
         <v>3</v>
       </c>
@@ -2613,7 +2613,7 @@
       </c>
     </row>
     <row r="32" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B32" s="17"/>
+      <c r="B32" s="15"/>
       <c r="C32" s="13">
         <v>6</v>
       </c>
@@ -2717,7 +2717,7 @@
       </c>
     </row>
     <row r="34" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B34" s="19" t="s">
+      <c r="B34" s="17" t="s">
         <v>15</v>
       </c>
       <c r="C34" s="13">
@@ -2770,7 +2770,7 @@
       </c>
     </row>
     <row r="35" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B35" s="19"/>
+      <c r="B35" s="17"/>
       <c r="C35" s="13">
         <v>7</v>
       </c>
@@ -2821,7 +2821,7 @@
       </c>
     </row>
     <row r="36" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B36" s="19"/>
+      <c r="B36" s="17"/>
       <c r="C36" s="13">
         <v>5</v>
       </c>
@@ -2872,7 +2872,7 @@
       </c>
     </row>
     <row r="37" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B37" s="19"/>
+      <c r="B37" s="17"/>
       <c r="C37" s="13">
         <v>7</v>
       </c>
@@ -2976,7 +2976,7 @@
       </c>
     </row>
     <row r="39" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B39" s="17" t="s">
+      <c r="B39" s="15" t="s">
         <v>16</v>
       </c>
       <c r="C39" s="13">
@@ -3029,7 +3029,7 @@
       </c>
     </row>
     <row r="40" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B40" s="17"/>
+      <c r="B40" s="15"/>
       <c r="C40" s="13">
         <v>11</v>
       </c>
@@ -3080,7 +3080,7 @@
       </c>
     </row>
     <row r="41" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B41" s="17"/>
+      <c r="B41" s="15"/>
       <c r="C41" s="13">
         <v>10</v>
       </c>
@@ -3131,7 +3131,7 @@
       </c>
     </row>
     <row r="42" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B42" s="17"/>
+      <c r="B42" s="15"/>
       <c r="C42" s="13">
         <v>11</v>
       </c>
@@ -3236,11 +3236,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="B4:B7"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="G2:J2"/>
-    <mergeCell ref="K2:N2"/>
     <mergeCell ref="O2:R2"/>
     <mergeCell ref="B39:B42"/>
     <mergeCell ref="B9:B12"/>
@@ -3249,6 +3244,11 @@
     <mergeCell ref="B24:B27"/>
     <mergeCell ref="B29:B32"/>
     <mergeCell ref="B34:B37"/>
+    <mergeCell ref="B4:B7"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="G2:J2"/>
+    <mergeCell ref="K2:N2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
